--- a/output/charts/prices_low_demand_annual_NSWDC.xlsx
+++ b/output/charts/prices_low_demand_annual_NSWDC.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>x</t>
   </si>
@@ -43,7 +43,10 @@
     <t>Sydney</t>
   </si>
   <si>
-    <t>Volume-weighted avg</t>
+    <t>Domestic volume-weighted avg</t>
+  </si>
+  <si>
+    <t>Volume-weighted avg incl. LNG exports</t>
   </si>
   <si>
     <t>2025-01-01T00:00:00.000000</t>
@@ -453,10 +456,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -487,837 +490,918 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2">
-        <v>5.361370086669922</v>
+        <v>7.410809516906738</v>
       </c>
       <c r="C2">
-        <v>5.891506671905518</v>
+        <v>9.188604354858398</v>
       </c>
       <c r="D2">
-        <v>5.361370086669922</v>
+        <v>7.366482734680176</v>
       </c>
       <c r="E2">
-        <v>6.900000095367432</v>
+        <v>6.961881160736084</v>
       </c>
       <c r="F2">
-        <v>5.361370086669922</v>
+        <v>7.38060998916626</v>
       </c>
       <c r="G2">
-        <v>5.596986293792725</v>
+        <v>8.220678329467773</v>
       </c>
       <c r="H2">
-        <v>5.361370086669922</v>
+        <v>8.043709754943848</v>
       </c>
       <c r="I2">
-        <v>5.961369514465332</v>
+        <v>9.36160945892334</v>
       </c>
       <c r="J2">
-        <v>5.509842872619629</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>8.896917343139648</v>
+      </c>
+      <c r="K2">
+        <v>7.936830043792725</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3">
-        <v>5.792876243591309</v>
+        <v>7.892697334289551</v>
       </c>
       <c r="C3">
-        <v>6.346575260162354</v>
+        <v>9.682479858398438</v>
       </c>
       <c r="D3">
-        <v>5.792876243591309</v>
+        <v>7.842258930206299</v>
       </c>
       <c r="E3">
-        <v>6.900000095367432</v>
+        <v>7.015773296356201</v>
       </c>
       <c r="F3">
-        <v>5.792876243591309</v>
+        <v>7.862497329711914</v>
       </c>
       <c r="G3">
-        <v>6.149862766265869</v>
+        <v>8.703690528869629</v>
       </c>
       <c r="H3">
-        <v>5.792876243591309</v>
+        <v>8.52559757232666</v>
       </c>
       <c r="I3">
-        <v>6.39232873916626</v>
+        <v>9.838639259338379</v>
       </c>
       <c r="J3">
-        <v>5.951162338256836</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>9.492985725402832</v>
+      </c>
+      <c r="K3">
+        <v>8.443072319030762</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>5.915890693664551</v>
+        <v>8.340721130371094</v>
       </c>
       <c r="C4">
-        <v>6.425205230712891</v>
+        <v>9.89442253112793</v>
       </c>
       <c r="D4">
-        <v>5.915890693664551</v>
+        <v>8.257020950317383</v>
       </c>
       <c r="E4">
-        <v>6.900000095367432</v>
+        <v>7.020107746124268</v>
       </c>
       <c r="F4">
-        <v>5.915890693664551</v>
+        <v>8.310521125793457</v>
       </c>
       <c r="G4">
-        <v>6.289588928222656</v>
+        <v>9.019991874694824</v>
       </c>
       <c r="H4">
-        <v>5.915890693664551</v>
+        <v>8.973621368408203</v>
       </c>
       <c r="I4">
-        <v>6.515342712402344</v>
+        <v>10.04665660858154</v>
       </c>
       <c r="J4">
-        <v>6.060110569000244</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>9.869270324707031</v>
+      </c>
+      <c r="K4">
+        <v>8.860743522644043</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>6.36164379119873</v>
+        <v>8.674771308898926</v>
       </c>
       <c r="C5">
-        <v>6.729588985443115</v>
+        <v>9.810760498046875</v>
       </c>
       <c r="D5">
-        <v>6.36164379119873</v>
+        <v>8.591071128845215</v>
       </c>
       <c r="E5">
-        <v>9.915068626403809</v>
+        <v>6.955152988433838</v>
       </c>
       <c r="F5">
-        <v>6.36164379119873</v>
+        <v>8.644570350646973</v>
       </c>
       <c r="G5">
-        <v>6.453972339630127</v>
+        <v>9.103702545166016</v>
       </c>
       <c r="H5">
-        <v>6.36164379119873</v>
+        <v>9.307671546936035</v>
       </c>
       <c r="I5">
-        <v>6.868218898773193</v>
+        <v>10.19652462005615</v>
       </c>
       <c r="J5">
-        <v>6.506037712097168</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>9.889863967895508</v>
+      </c>
+      <c r="K5">
+        <v>9.115311622619629</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6">
-        <v>6.658904075622559</v>
+        <v>14.62377834320068</v>
       </c>
       <c r="C6">
-        <v>7.085479259490967</v>
+        <v>14.18805503845215</v>
       </c>
       <c r="D6">
-        <v>6.658904075622559</v>
+        <v>14.54007911682129</v>
       </c>
       <c r="E6">
-        <v>9.964109420776367</v>
+        <v>10.18943881988525</v>
       </c>
       <c r="F6">
-        <v>6.658904075622559</v>
+        <v>14.59357833862305</v>
       </c>
       <c r="G6">
-        <v>6.985753536224365</v>
+        <v>13.72632312774658</v>
       </c>
       <c r="H6">
-        <v>6.658904075622559</v>
+        <v>15.25667953491211</v>
       </c>
       <c r="I6">
-        <v>7.380274295806885</v>
+        <v>14.5708646774292</v>
       </c>
       <c r="J6">
-        <v>6.931436538696289</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>14.78867530822754</v>
+      </c>
+      <c r="K6">
+        <v>14.80207824707031</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7">
-        <v>7.190958976745605</v>
+        <v>12.47990131378174</v>
       </c>
       <c r="C7">
-        <v>7.753424644470215</v>
+        <v>13.11913013458252</v>
       </c>
       <c r="D7">
-        <v>7.190958976745605</v>
+        <v>12.39620208740234</v>
       </c>
       <c r="E7">
-        <v>10.43863010406494</v>
+        <v>8.84950065612793</v>
       </c>
       <c r="F7">
-        <v>7.190958976745605</v>
+        <v>12.4497013092041</v>
       </c>
       <c r="G7">
-        <v>7.704383850097656</v>
+        <v>13.00993728637695</v>
       </c>
       <c r="H7">
-        <v>7.190958976745605</v>
+        <v>13.11280059814453</v>
       </c>
       <c r="I7">
-        <v>8.071781158447266</v>
+        <v>13.20309543609619</v>
       </c>
       <c r="J7">
-        <v>7.532122135162354</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>13.23146629333496</v>
+      </c>
+      <c r="K7">
+        <v>12.82925891876221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
-        <v>7.723197460174561</v>
+        <v>12.83458805084229</v>
       </c>
       <c r="C8">
-        <v>8.025205612182617</v>
+        <v>13.77233028411865</v>
       </c>
       <c r="D8">
-        <v>7.723197460174561</v>
+        <v>12.75088787078857</v>
       </c>
       <c r="E8">
-        <v>10.94821834564209</v>
+        <v>9.228819847106934</v>
       </c>
       <c r="F8">
-        <v>7.723197460174561</v>
+        <v>12.80438804626465</v>
       </c>
       <c r="G8">
-        <v>8.237534523010254</v>
+        <v>14.06526660919189</v>
       </c>
       <c r="H8">
-        <v>7.723197460174561</v>
+        <v>13.46748733520508</v>
       </c>
       <c r="I8">
-        <v>8.670411109924316</v>
+        <v>13.62315940856934</v>
       </c>
       <c r="J8">
-        <v>8.063604354858398</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>13.91415405273438</v>
+      </c>
+      <c r="K8">
+        <v>13.2623929977417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
-        <v>7.780706882476807</v>
+        <v>13.15074920654297</v>
       </c>
       <c r="C9">
-        <v>7.810958862304688</v>
+        <v>13.66727352142334</v>
       </c>
       <c r="D9">
-        <v>7.780706882476807</v>
+        <v>13.06704998016357</v>
       </c>
       <c r="E9">
-        <v>10.99095916748047</v>
+        <v>9.242379188537598</v>
       </c>
       <c r="F9">
-        <v>7.780706882476807</v>
+        <v>13.12054920196533</v>
       </c>
       <c r="G9">
-        <v>7.974520206451416</v>
+        <v>14.0137414932251</v>
       </c>
       <c r="H9">
-        <v>7.780706882476807</v>
+        <v>13.78364849090576</v>
       </c>
       <c r="I9">
-        <v>8.420547485351562</v>
+        <v>13.6339807510376</v>
       </c>
       <c r="J9">
-        <v>8.002254486083984</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>13.83970355987549</v>
+      </c>
+      <c r="K9">
+        <v>13.48319816589355</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
-        <v>7.795616149902344</v>
+        <v>12.75926399230957</v>
       </c>
       <c r="C10">
-        <v>7.836920738220215</v>
+        <v>13.39065742492676</v>
       </c>
       <c r="D10">
-        <v>7.795616149902344</v>
+        <v>12.67556476593018</v>
       </c>
       <c r="E10">
-        <v>11.016921043396</v>
+        <v>8.97675609588623</v>
       </c>
       <c r="F10">
-        <v>7.795616149902344</v>
+        <v>12.72906398773193</v>
       </c>
       <c r="G10">
-        <v>8.096098899841309</v>
+        <v>13.54154109954834</v>
       </c>
       <c r="H10">
-        <v>7.795616149902344</v>
+        <v>13.392165184021</v>
       </c>
       <c r="I10">
-        <v>8.556920051574707</v>
+        <v>13.36835670471191</v>
       </c>
       <c r="J10">
-        <v>8.048632621765137</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>13.50090980529785</v>
+      </c>
+      <c r="K10">
+        <v>13.10299301147461</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11">
-        <v>7.842311859130859</v>
+        <v>12.82716464996338</v>
       </c>
       <c r="C11">
-        <v>8.013676643371582</v>
+        <v>13.47100925445557</v>
       </c>
       <c r="D11">
-        <v>7.842311859130859</v>
+        <v>12.74346542358398</v>
       </c>
       <c r="E11">
-        <v>11.08669567108154</v>
+        <v>9.045173645019531</v>
       </c>
       <c r="F11">
-        <v>7.842311859130859</v>
+        <v>12.79696464538574</v>
       </c>
       <c r="G11">
-        <v>8.383079528808594</v>
+        <v>13.60210037231445</v>
       </c>
       <c r="H11">
-        <v>7.842311859130859</v>
+        <v>13.46006488800049</v>
       </c>
       <c r="I11">
-        <v>8.844799995422363</v>
+        <v>13.43625736236572</v>
       </c>
       <c r="J11">
-        <v>8.169801712036133</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>13.62178325653076</v>
+      </c>
+      <c r="K11">
+        <v>13.18082046508789</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12">
-        <v>7.843424797058105</v>
+        <v>12.87842845916748</v>
       </c>
       <c r="C12">
-        <v>8.16860294342041</v>
+        <v>13.74300479888916</v>
       </c>
       <c r="D12">
-        <v>7.843424797058105</v>
+        <v>12.79472827911377</v>
       </c>
       <c r="E12">
-        <v>11.09602737426758</v>
+        <v>15.85297107696533</v>
       </c>
       <c r="F12">
-        <v>7.843424797058105</v>
+        <v>12.84822845458984</v>
       </c>
       <c r="G12">
-        <v>8.74419116973877</v>
+        <v>13.99358177185059</v>
       </c>
       <c r="H12">
-        <v>7.843424797058105</v>
+        <v>13.51132774353027</v>
       </c>
       <c r="I12">
-        <v>9.19160270690918</v>
+        <v>13.67178821563721</v>
       </c>
       <c r="J12">
-        <v>8.27845573425293</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>14.25035190582275</v>
+      </c>
+      <c r="K12">
+        <v>13.36594486236572</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13">
-        <v>7.857797145843506</v>
+        <v>12.01166343688965</v>
       </c>
       <c r="C13">
-        <v>7.905704021453857</v>
+        <v>13.01731300354004</v>
       </c>
       <c r="D13">
-        <v>7.857797145843506</v>
+        <v>11.92796325683594</v>
       </c>
       <c r="E13">
-        <v>11.12026309967041</v>
+        <v>15.06986331939697</v>
       </c>
       <c r="F13">
-        <v>7.857797145843506</v>
+        <v>11.98146438598633</v>
       </c>
       <c r="G13">
-        <v>8.412821769714355</v>
+        <v>13.29943370819092</v>
       </c>
       <c r="H13">
-        <v>7.857797145843506</v>
+        <v>12.64456367492676</v>
       </c>
       <c r="I13">
-        <v>8.851150512695312</v>
+        <v>12.96631240844727</v>
       </c>
       <c r="J13">
-        <v>8.170138359069824</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>13.3549222946167</v>
+      </c>
+      <c r="K13">
+        <v>12.52233695983887</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14">
-        <v>7.859676837921143</v>
+        <v>12.06260681152344</v>
       </c>
       <c r="C14">
-        <v>7.858254432678223</v>
+        <v>12.95009994506836</v>
       </c>
       <c r="D14">
-        <v>7.859676837921143</v>
+        <v>11.97890663146973</v>
       </c>
       <c r="E14">
-        <v>11.11721134185791</v>
+        <v>15.12080764770508</v>
       </c>
       <c r="F14">
-        <v>7.859676837921143</v>
+        <v>12.0324068069458</v>
       </c>
       <c r="G14">
-        <v>8.408763885498047</v>
+        <v>13.25390625</v>
       </c>
       <c r="H14">
-        <v>7.859676837921143</v>
+        <v>12.69550800323486</v>
       </c>
       <c r="I14">
-        <v>8.843085289001465</v>
+        <v>12.98237609863281</v>
       </c>
       <c r="J14">
-        <v>8.177058219909668</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>13.33844661712646</v>
+      </c>
+      <c r="K14">
+        <v>12.54910182952881</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15">
-        <v>7.783999919891357</v>
+        <v>12.09010696411133</v>
       </c>
       <c r="C15">
-        <v>7.830202579498291</v>
+        <v>12.89715480804443</v>
       </c>
       <c r="D15">
-        <v>7.783999919891357</v>
+        <v>12.00640773773193</v>
       </c>
       <c r="E15">
-        <v>11.05304145812988</v>
+        <v>15.14830780029297</v>
       </c>
       <c r="F15">
-        <v>7.783999919891357</v>
+        <v>12.05990695953369</v>
       </c>
       <c r="G15">
-        <v>8.126564979553223</v>
+        <v>13.17893314361572</v>
       </c>
       <c r="H15">
-        <v>7.783999919891357</v>
+        <v>12.72300815582275</v>
       </c>
       <c r="I15">
-        <v>8.557117462158203</v>
+        <v>12.96069812774658</v>
       </c>
       <c r="J15">
-        <v>8.027618408203125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>13.22829723358154</v>
+      </c>
+      <c r="K15">
+        <v>12.53225517272949</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16">
-        <v>7.706999778747559</v>
+        <v>12.06086349487305</v>
       </c>
       <c r="C16">
-        <v>7.764991760253906</v>
+        <v>12.86256313323975</v>
       </c>
       <c r="D16">
-        <v>7.706999778747559</v>
+        <v>11.97716331481934</v>
       </c>
       <c r="E16">
-        <v>10.95083522796631</v>
+        <v>15.11906337738037</v>
       </c>
       <c r="F16">
-        <v>7.706999778747559</v>
+        <v>12.03066444396973</v>
       </c>
       <c r="G16">
-        <v>7.644035816192627</v>
+        <v>13.14076232910156</v>
       </c>
       <c r="H16">
-        <v>7.706999778747559</v>
+        <v>12.69376373291016</v>
       </c>
       <c r="I16">
-        <v>8.109810829162598</v>
+        <v>12.92683410644531</v>
       </c>
       <c r="J16">
-        <v>7.832610130310059</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>13.18928718566895</v>
+      </c>
+      <c r="K16">
+        <v>12.48874664306641</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17">
-        <v>7.62999963760376</v>
+        <v>12.05273342132568</v>
       </c>
       <c r="C17">
-        <v>7.690273761749268</v>
+        <v>12.81564617156982</v>
       </c>
       <c r="D17">
-        <v>7.62999963760376</v>
+        <v>11.96903228759766</v>
       </c>
       <c r="E17">
-        <v>10.87317752838135</v>
+        <v>15.11093235015869</v>
       </c>
       <c r="F17">
-        <v>7.62999963760376</v>
+        <v>12.02253341674805</v>
       </c>
       <c r="G17">
-        <v>7.459616661071777</v>
+        <v>13.0937032699585</v>
       </c>
       <c r="H17">
-        <v>7.62999963760376</v>
+        <v>12.68563270568848</v>
       </c>
       <c r="I17">
-        <v>7.889726161956787</v>
+        <v>12.91773223876953</v>
       </c>
       <c r="J17">
-        <v>7.712938785552979</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>13.15229606628418</v>
+      </c>
+      <c r="K17">
+        <v>12.46662330627441</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18">
-        <v>7.578999996185303</v>
+        <v>10.74363994598389</v>
       </c>
       <c r="C18">
-        <v>7.654613971710205</v>
+        <v>12.390944480896</v>
       </c>
       <c r="D18">
-        <v>7.578999996185303</v>
+        <v>10.65993976593018</v>
       </c>
       <c r="E18">
-        <v>10.83723831176758</v>
+        <v>13.98253440856934</v>
       </c>
       <c r="F18">
-        <v>7.578999996185303</v>
+        <v>10.71344089508057</v>
       </c>
       <c r="G18">
-        <v>7.803690433502197</v>
+        <v>12.79094314575195</v>
       </c>
       <c r="H18">
-        <v>7.578999996185303</v>
+        <v>11.37654113769531</v>
       </c>
       <c r="I18">
-        <v>8.237934112548828</v>
+        <v>11.90548706054688</v>
       </c>
       <c r="J18">
-        <v>7.780752182006836</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>12.60967445373535</v>
+      </c>
+      <c r="K18">
+        <v>11.38681697845459</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19">
-        <v>7.527999877929688</v>
+        <v>11.10940742492676</v>
       </c>
       <c r="C19">
-        <v>7.609578132629395</v>
+        <v>12.36177349090576</v>
       </c>
       <c r="D19">
-        <v>7.527999877929688</v>
+        <v>11.02570629119873</v>
       </c>
       <c r="E19">
-        <v>10.79544067382812</v>
+        <v>14.29434013366699</v>
       </c>
       <c r="F19">
-        <v>7.527999877929688</v>
+        <v>11.0792064666748</v>
       </c>
       <c r="G19">
-        <v>7.438004970550537</v>
+        <v>12.7613525390625</v>
       </c>
       <c r="H19">
-        <v>7.527999877929688</v>
+        <v>11.74230670928955</v>
       </c>
       <c r="I19">
-        <v>7.82470178604126</v>
+        <v>12.12916278839111</v>
       </c>
       <c r="J19">
-        <v>7.617737293243408</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>12.64475917816162</v>
+      </c>
+      <c r="K19">
+        <v>11.65519428253174</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20">
-        <v>7.476999759674072</v>
+        <v>11.30366039276123</v>
       </c>
       <c r="C20">
-        <v>7.465290546417236</v>
+        <v>12.36360931396484</v>
       </c>
       <c r="D20">
-        <v>7.476999759674072</v>
+        <v>11.21996021270752</v>
       </c>
       <c r="E20">
-        <v>10.64529037475586</v>
+        <v>14.41034126281738</v>
       </c>
       <c r="F20">
-        <v>7.476999759674072</v>
+        <v>11.27346038818359</v>
       </c>
       <c r="G20">
-        <v>7.279582977294922</v>
+        <v>12.76276397705078</v>
       </c>
       <c r="H20">
-        <v>7.476999759674072</v>
+        <v>11.93655967712402</v>
       </c>
       <c r="I20">
-        <v>7.643646240234375</v>
+        <v>12.23030185699463</v>
       </c>
       <c r="J20">
-        <v>7.533880710601807</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>12.69387626647949</v>
+      </c>
+      <c r="K20">
+        <v>11.80380058288574</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21">
-        <v>7.426000118255615</v>
+        <v>11.47593212127686</v>
       </c>
       <c r="C21">
-        <v>7.457046508789062</v>
+        <v>12.35310745239258</v>
       </c>
       <c r="D21">
-        <v>7.426000118255615</v>
+        <v>11.39223289489746</v>
       </c>
       <c r="E21">
-        <v>10.63704681396484</v>
+        <v>14.55463695526123</v>
       </c>
       <c r="F21">
-        <v>7.426000118255615</v>
+        <v>11.44573211669922</v>
       </c>
       <c r="G21">
-        <v>7.317862987518311</v>
+        <v>12.74884986877441</v>
       </c>
       <c r="H21">
-        <v>7.426000118255615</v>
+        <v>12.10883331298828</v>
       </c>
       <c r="I21">
-        <v>7.713758945465088</v>
+        <v>12.36143684387207</v>
       </c>
       <c r="J21">
-        <v>7.511330604553223</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>12.72178745269775</v>
+      </c>
+      <c r="K21">
+        <v>11.93592166900635</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22">
-        <v>7.375</v>
+        <v>11.57607650756836</v>
       </c>
       <c r="C22">
-        <v>7.514863014221191</v>
+        <v>12.32119941711426</v>
       </c>
       <c r="D22">
-        <v>7.375</v>
+        <v>11.49237632751465</v>
       </c>
       <c r="E22">
-        <v>10.70993137359619</v>
+        <v>14.64079093933105</v>
       </c>
       <c r="F22">
-        <v>7.375</v>
+        <v>11.54587745666504</v>
       </c>
       <c r="G22">
-        <v>7.382876873016357</v>
+        <v>12.72111797332764</v>
       </c>
       <c r="H22">
-        <v>7.375</v>
+        <v>12.20897674560547</v>
       </c>
       <c r="I22">
-        <v>7.783629894256592</v>
+        <v>12.44759082794189</v>
       </c>
       <c r="J22">
-        <v>7.486600875854492</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>12.73532867431641</v>
+      </c>
+      <c r="K22">
+        <v>12.01050567626953</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23">
-        <v>7.323999881744385</v>
+        <v>11.61651420593262</v>
       </c>
       <c r="C23">
-        <v>7.500536918640137</v>
+        <v>12.34090614318848</v>
       </c>
       <c r="D23">
-        <v>7.323999881744385</v>
+        <v>11.53281497955322</v>
       </c>
       <c r="E23">
-        <v>10.69587898254395</v>
+        <v>14.67471504211426</v>
       </c>
       <c r="F23">
-        <v>7.323999881744385</v>
+        <v>11.5863151550293</v>
       </c>
       <c r="G23">
-        <v>7.375682353973389</v>
+        <v>12.74090576171875</v>
       </c>
       <c r="H23">
-        <v>7.323999881744385</v>
+        <v>12.24941444396973</v>
       </c>
       <c r="I23">
-        <v>7.808701515197754</v>
+        <v>12.4820671081543</v>
       </c>
       <c r="J23">
-        <v>7.449991226196289</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>12.74900436401367</v>
+      </c>
+      <c r="K23">
+        <v>12.04438018798828</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24">
-        <v>7.273000240325928</v>
+        <v>11.69007396697998</v>
       </c>
       <c r="C24">
-        <v>7.484884738922119</v>
+        <v>12.39484596252441</v>
       </c>
       <c r="D24">
-        <v>7.273000240325928</v>
+        <v>11.60637474060059</v>
       </c>
       <c r="E24">
-        <v>10.67720794677734</v>
+        <v>14.7482738494873</v>
       </c>
       <c r="F24">
-        <v>7.273000240325928</v>
+        <v>11.65987396240234</v>
       </c>
       <c r="G24">
-        <v>7.406197071075439</v>
+        <v>12.79400253295898</v>
       </c>
       <c r="H24">
-        <v>7.273000240325928</v>
+        <v>12.32297420501709</v>
       </c>
       <c r="I24">
-        <v>7.829432487487793</v>
+        <v>12.55562782287598</v>
       </c>
       <c r="J24">
-        <v>7.416871070861816</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>12.79125213623047</v>
+      </c>
+      <c r="K24">
+        <v>12.11076927185059</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25">
-        <v>7.222000122070312</v>
+        <v>11.71042823791504</v>
       </c>
       <c r="C25">
-        <v>7.46939754486084</v>
+        <v>12.41769695281982</v>
       </c>
       <c r="D25">
-        <v>7.222000122070312</v>
+        <v>11.62672805786133</v>
       </c>
       <c r="E25">
-        <v>10.65975856781006</v>
+        <v>14.76862812042236</v>
       </c>
       <c r="F25">
-        <v>7.222000122070312</v>
+        <v>11.6802282333374</v>
       </c>
       <c r="G25">
-        <v>7.433429718017578</v>
+        <v>12.81601142883301</v>
       </c>
       <c r="H25">
-        <v>7.222000122070312</v>
+        <v>12.34332847595215</v>
       </c>
       <c r="I25">
-        <v>7.851665496826172</v>
+        <v>12.57579708099365</v>
       </c>
       <c r="J25">
-        <v>7.384239673614502</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>12.80007553100586</v>
+      </c>
+      <c r="K25">
+        <v>12.12870979309082</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26">
-        <v>7.171000003814697</v>
+        <v>11.69363784790039</v>
       </c>
       <c r="C26">
-        <v>7.456717491149902</v>
+        <v>12.41641521453857</v>
       </c>
       <c r="D26">
-        <v>7.171000003814697</v>
+        <v>11.609938621521</v>
       </c>
       <c r="E26">
-        <v>10.64469337463379</v>
+        <v>14.75183773040771</v>
       </c>
       <c r="F26">
-        <v>7.171000003814697</v>
+        <v>11.66343784332275</v>
       </c>
       <c r="G26">
-        <v>7.422120571136475</v>
+        <v>12.81472969055176</v>
       </c>
       <c r="H26">
-        <v>7.171000003814697</v>
+        <v>12.3265380859375</v>
       </c>
       <c r="I26">
-        <v>7.877383232116699</v>
+        <v>12.55696868896484</v>
       </c>
       <c r="J26">
-        <v>7.348194599151611</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>12.78943061828613</v>
+      </c>
+      <c r="K26">
+        <v>12.11353397369385</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27">
-        <v>7.12000036239624</v>
+        <v>11.69644165039062</v>
       </c>
       <c r="C27">
-        <v>7.444438457489014</v>
+        <v>12.41918468475342</v>
       </c>
       <c r="D27">
-        <v>7.12000036239624</v>
+        <v>11.61274242401123</v>
       </c>
       <c r="E27">
-        <v>10.62679481506348</v>
+        <v>14.75464248657227</v>
       </c>
       <c r="F27">
-        <v>7.12000036239624</v>
+        <v>11.66624164581299</v>
       </c>
       <c r="G27">
-        <v>7.448328495025635</v>
+        <v>12.8174991607666</v>
       </c>
       <c r="H27">
-        <v>7.12000036239624</v>
+        <v>12.32934188842773</v>
       </c>
       <c r="I27">
-        <v>7.899725914001465</v>
+        <v>12.54542350769043</v>
       </c>
       <c r="J27">
-        <v>7.316247940063477</v>
+        <v>12.79653072357178</v>
+      </c>
+      <c r="K27">
+        <v>12.11744117736816</v>
       </c>
     </row>
   </sheetData>
